--- a/Instagram/PAVLOV_content_plan.xlsx
+++ b/Instagram/PAVLOV_content_plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как пользоваться" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Plan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Как пользоваться" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="65" customHeight="1">
+    <row r="2" ht="100.8" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -565,120 +565,121 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Сетка · закрепить</t>
+          <t>Сетка · поз. 1 · закрепить</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Главный визуал. Доказать, что объекты настоящие и красивые</t>
+          <t>Происхождение бренда. Кто это и почему вообще появилось</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>Свои объекты вместе: общий вид двора, терраса вечером, домик днём, сауна снаружи, крупный узел. 5–6 кадров, первый — двор целиком, чтобы было видно, что всё это одно место</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Nie znalazłem na rynku tego, czego szukałem. Więc zbudowałem sam.
+Taras z jacuzzi i kinem. Domek dla córek. Sauna. Wszystko na własnym podwórku — od pierwszego szkicu po zapalone światło.
+Jestem pierwszym klientem.</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>«Zaczynam od siebie. Dosłownie.»</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="100.8" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>KARUZELA</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · поз. 2 · закрепить</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Доказательство вкуса и уровня. Главный визуал</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>Терраса: все кадры одной каруселью — общий вечерний, золотой час с джакузи, интерьер с обогревателем, халат и вид в сад, ночной с экраном. 5–6 кадров, первый самый сильный</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Na rynku nie znalazłem rozwiązania, które łączyłoby jacuzzi, kino i wygodną strefę wypoczynku na 1,8 × 4,8 m. Zaprojektowałem więc własne.
 Rano kawa, w południe dzieci w wodzie, wieczorem film. Cały ogród robi się ciemny, a tutaj pali się światło.
 Nikt nigdzie nie jedzie.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Последний кадр: «Co byś tu dodał?»</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="65" customHeight="1">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>«Co byś tu dodał?»</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="75.59999999999999" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>KARUZELA</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Сетка · закрепить</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · поз. 3</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Второе направление. Показать, что это не единичный объект</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Домик: общий дневной, от дома, интерьер со столиком, вечерний со светом, качели снизу. 5 кадров</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Zwykle trzeba wybrać: albo tanio, albo ładnie, albo na lata. Budowałem dla córek, więc nie wybierałem.
 2 × 3,6 m. Grafit i modrzew. Poziome elementy zakryte obróbkami blacharskimi, schody schowane pod konstrukcją. Nic nie gnije.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>«Domek czy altana — co pierwsze?»</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>KARUZELA</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Сетка · закрепить</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Третье направление + доказательство диапазона</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Баня снаружи: 3–4 кадра общих. Внутрь не заходим, отделка не закончена</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Sauna stoi obok altany. Ten sam język: grafit na zewnątrz, drewno w środku.
-Wnętrze jeszcze w robocie — pokażę, kiedy skończę.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>«Co powinno być w saunie ogrodowej?»</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="65" customHeight="1">
+    <row r="5" ht="151.2" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -689,188 +690,317 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Сетка</t>
+          <t>Сетка · поз. 4 · закрепить</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>КОММЕРЧЕСКОЕ ЯДРО. Единственный пост, который прямо говорит, что можно заказать сейчас</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Карточки с текстом на фоне своих объектов + кадр эскиза от руки + один кадр рабочего процесса. 5–6 кадров. Верстать спокойно, без рекламной графики и без процентов скидки</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Na najbliższe pół roku przyjmuję 2–3 projekty. Tyle, ile mogę poprowadzić sam — od pomysłu po ostatni detal.
+Pomysł → projekt → dopasowanie do budżetu → materiały → wykonanie → wyposażenie → gotowe miejsce.
+To pierwsze realizacje PAVLOV u klientów, więc warunki są startowe. Taki obiekt, składany przez kilka firm, kosztuje zwykle 20–25 tysięcy. U mnie teraz — 13–18.
+Nie taniej za to samo. Taniej, bo między hurtownią a Twoją działką nikt nie dolicza swojego.</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>«Masz pomysł? Napisz.»</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88.2" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>KARUZELA</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · поз. 5</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>Экспертиза. Показать мышление, а не объект</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Лестница: кадр снизу под домиком, крупный план узла, для контраста — как выглядит наружная лестница через пару лет (без указания на чужой объект)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>W większości domków schody dostawia się z zewnątrz. Po kilku sezonach są do wymiany.
 Tutaj schowałem je pod konstrukcją, w suchym miejscu. Poziome elementy zakryte obróbkami blacharskimi — tak jak dach.
 Tego nie widać na zdjęciach. Widać za trzy lata.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>«Zapisz, jeśli planujesz domek»</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75.59999999999999" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>KARUZELA</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Сетка</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · поз. 6</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Главный дифференциатор — полная комплектация</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Что входит: по кадру на позицию — конструкция, пол, крыша, шторы, гирлянды, обогреватель, мебель, джакузи, проектор, растения, декор. 10–12 кадров</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Konkurencja sprzedaje konstrukcję. Resztę dokupujesz sam — meble, światło, tekstylia, zieleń.
+U mnie to jeden komplet. Od pomysłu po zapalone światło.
+Nic do dokupienia. Nic do dokończenia.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>«Czego brakuje na Twoim tarasie?»</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="163.8" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>KARUZELA</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · поз. 7</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Аргумент цены. Почему один человек выходит дешевле цепочки — без процентов скидки</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>По кадру на роль: эскиз, каркас, доборники на горизонталях, электрика, посадка растений, мебель. Финальный кадр — готовое место целиком. 7 кадров</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Żeby powstało takie miejsce, zwykle potrzeba sześciu osób.
+Projektant narysuje. Cieśla postawi konstrukcję. Blacharz zrobi obróbki. Elektryk doprowadzi światło. Ktoś posadzi zieleń. Ktoś dobierze meble i tekstylia.
+Sześć terminów, sześć rozmów, sześć marż — i nikt nie odpowiada za całość, każdy za swój kawałek.
+U mnie materiały idą po cenie zakupu, z paragonami, a moja praca to kwota ustalona przed startem.
+Jeden wykonawca. Bez pośredników.</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>«Ile z tych sześciu masz już znalezionych?»</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88.2" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>KARUZELA</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · поз. 8</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Деталь как доказательство «каждая деталь продумана»</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Кашпо: общий вид с растениями, крупно дно с туевыми ветками, схема посадки — хвойные внизу, плющ вверху</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Donice zbiłem sam. Iglaki na dole, bluszcz i barwinek wyżej, dno wyłożone gałęziami tui — woda spływa, a korzenie nie marzną.
 Zielone przez cały rok, także zimą.
 Zieleń nie jest dodatkiem: łagodzi grafitową geometrię.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>«Zapisz na wiosnę»</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="126" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>KARUZELA</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Сетка</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Главный дифференциатор — полная комплектация</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Что входит: по кадру на позицию — конструкция, пол, крыша, шторы, гирлянды, обогреватель, мебель, джакузи, проектор, растения, декор. 10–12 кадров</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Konkurencja sprzedaje konstrukcję. Resztę dokupujesz sam — meble, światło, tekstylia, zieleń.
-U mnie to jeden komplet. Od pomysłu po zapalone światło.
-Nic do dokupienia. Nic do dokończenia.</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>«Czego brakuje na Twoim tarasie?»</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>KARUZELA</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Сетка</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Механика Pinterest. Объяснить, как работает заказ</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · поз. 9</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Механика заказа + прямой вход. Достаточно одной картинки</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Pinterest vs реальность: скрин картинки с доски, промежуточный эскиз, фото реализации. 3–4 кадра</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Zdjęcie z Pinteresta to punkt wyjścia, nie projekt. Inny klimat, inne materiały, inne ceny.
 Adaptuję pomysł pod konkretną działkę i budżet — i dopiero wtedy powstaje coś, co da się zbudować.
-Wystarczy jeden obraz, żeby zacząć.</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+Wystarczy jeden obraz, żeby zacząć.
+Piękny pomysł szuka swojego gospodarza. Mam miejsce na dwa, może trzy, w tym półroczu.</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>«Wyślij swój obraz»</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>KARUZELA</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · позже</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Третье направление. НЕ входит в стартовые 9: фотографий бани нет ни одной, снимать</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Баня снаружи: 3–4 общих кадра. Внутрь не заходим, отделка не закончена</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Sauna stoi obok altany. Ten sam język: grafit na zewnątrz, drewno w środku.
+Wnętrze jeszcze w robocie — pokażę, kiedy skończę.</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>«Co powinno być w saunie ogrodowej?»</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>REELS</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Лента + сетка</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Холодный охват. Показать разрыв мечты и реальности</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Холодный охват. Разрыв мечты и реальности</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Pinterest → эскиз → реальность. Кадр 1: картинка с доски. Кадр 2: руки, эскиз на бумаге. Кадр 3: готовый объект. 15–20 сек, быстрая склейка</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>На экране:
 1) «Znalazłem to na Pinterest»
@@ -878,42 +1008,42 @@
 3) «I tak to wygląda naprawdę»</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>«Wyślij swój obraz — reszta moja»</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>→ Oferta: «Masz pomysł? Zaprojektuję go pod Twoje miejsce i budżet.»</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>REELS</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Лента + сетка</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Залипательный охват. Работает без слов</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Обжиг доски: горелка, дым, огонь, щётка снимает нагар, финал — фактура крупно. 15 сек</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>На экране:
 1) «Zwykła deska»
@@ -921,42 +1051,42 @@
 3) «Trzyma się 20 lat bez malowania»</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>«Zapisz — przyda się»</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>→ Oferta: «Nie każdy wykonawca podejmie się takiego projektu.»</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>REELS</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Лента + сетка</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Сохраняемость. Экспертиза в материалах</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Сохраняемость. Экспертиза в материалах. Здесь НЕ продаём — это доказательство</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Заметка о композите: рука на композитной доске в жару, термометр или просто отдёрнутая рука, рядом дерево. 20 сек</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>На экране:
 1) «Kompozyt w słońcu: 60°C»
@@ -964,86 +1094,86 @@
 3) «Dlatego na taras pod słońcem daję drewno»</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>«Zapisz, zanim kupisz deski»</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="63" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>REELS</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Лента + сетка</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Снять страх цены. Высокая сохраняемость</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Смета вслух: картинка с Pinterest на экране, поверх появляются диапазоны — конструкция, комплектация, монтаж. Итог диапазоном</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Снять страх цены. Показать абсолютную экономику, без процентов</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Смета вслух: картинка с Pinterest на экране, поверх появляются суммы. Итог диапазоном, без разбора по статьям</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>На экране:
-1) «Ile kosztuje taka altana?»
-2) «Konstrukcja: 8–11 tys.»
-3) «Z pełnym wyposażeniem: 19–24 tys.»
-4) «Pusta konstrukcja tej wielkości zaczyna się od 10 tys.»</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>«Napisz, policzę pod Twoją działkę»</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+1) «Ile kosztuje takie miejsce?»
+2) «Przez kilka firm: 20–25 tys.»
+3) «U mnie teraz: 13–18 tys.»
+4) «Bo nikt po drodze nie dolicza swojego»</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>→ Oferta: «Pierwsze realizacje PAVLOV — zanim portfolio urośnie. Napisz.»</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="63" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>REELS</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Лента + сетка</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Ответ на возражение «проще съездить в отель»</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Отель vs двор: кадры отеля/спа из стока или Pinterest, затем своя терраса вечером. Контраст цены</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Отель vs двор: кадры отеля или спа из стока, затем своя терраса вечером. Контраст цены</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>На экране:
 1) «Weekend w hotelu SPA: 1800 zł»
@@ -1052,42 +1182,42 @@
 4) «Do hotelu trzeba pojechać. Tu wystarczy wyjść.»</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>«Ile razy w roku wyjeżdżasz?»</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>→ Oferta: «Zaczynam od siebie. Teraz szukam kolejnych miejsc.»</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>REELS</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Лента + сетка</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Показать процесс изменений. До/после внутри ролика</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Процесс изменений. До/после внутри ролика</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Замена стенки или установка штор на террасе: до, процесс, после. Снимать с одной точки</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>На экране:
 1) «Wiatr wiał od zachodu»
@@ -1095,135 +1225,9 @@
 3) «I wieczory wróciły»</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>«Więcej realizacji na profilu»</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Кружок CENNIK</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Порог. Отсечь нецелевых до первого сообщения</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Карточка с текстом на фоне фото объекта</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Domki dla dzieci — od 16 000 zł
-Altany ogrodowe — od 19 000 zł
-To próg, nie cennik. Każdy projekt liczę osobno.</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Кружок CENNIK</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Дешёвый вход. Снять страх большой суммы</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Карточка + фото эскиза от руки</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Szkic koncepcyjny — 1000 zł
-Rysunek, główne wymiary, orientacyjny koszt realizacji.
-Jeśli robimy dalej — kwota wchodzi w cenę.</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Кружок CENNIK</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Снять подозрение. Показать механику цены</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Карточка + фото чеков или материалов на складе</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Materiały — po cenie zakupu, z paragonami.
-Moja praca — kwota ustalona przed startem.
-Między hurtownią a Twoją działką nikt nie dolicza swojego.</t>
-        </is>
-      </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ Oferta: «Jeden człowiek. Od pierwszego szkicu po montaż.»</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1232,7 +1236,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
+    <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1243,25 +1247,23 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Кружок CENNIK</t>
+          <t>Кружок OFERTA · 1</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Объяснить, за что платят одному человеку</t>
+          <t>Ограничение. Сразу сказать, сколько проектов и на какой срок</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Карточка со списком ролей</t>
+          <t>Карточка с текстом на фоне фото объекта</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Gdybyś składał to sam:
-projektant · cieśla · blacharz · elektryk · zagospodarowanie · wystrój
-Sześć osób, sześć terminów, sześć marż.
-Albo jedna umowa.</t>
+          <t>Na najbliższe pół roku przyjmuję 2–3 projekty.
+Tyle, ile mogę poprowadzić sam — od pomysłu po ostatni detal.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1286,20 +1288,310 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>Кружок OFERTA · 2</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Что именно происходит. Весь путь одной строкой</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Карточка со схемой пути</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Pomysł → projekt → dopasowanie do budżetu → materiały → wykonanie → wyposażenie → gotowe miejsce.
+Jedna osoba na każdym z tych kroków.</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="63" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>STORIS</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Кружок OFERTA · 3</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Что беру на себя лично. Снять вопрос «а что мне придётся делать самому»</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Карточка со списком + фото рабочего процесса</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Biorę na siebie: rysunek i wymiary, zakup materiału, konstrukcję, obróbki blacharskie, światło, zieleń, meble i tekstylia.
+Twoje jest tylko dwoje: pomysł i budżet.</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="88.2" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>STORIS</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Кружок OFERTA · 4</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Почему это не сравнить с местной фирмой. Отвести сравнение с альтаной за 2 000 zł</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Карточка + кадр сложного узла крупно</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>To nie jest standardowa oferta.
+Nie każdy projektant narysuje taki obiekt. Nie każdy wykonawca podejmie się nietypowych węzłów, wypalanego drewna, ukrytych schodów i elektryki naraz.
+Dlatego nie ma tego w żadnym cenniku.</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>STORIS</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Кружок OFERTA · 5</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Почему цена ниже будущей. Аргумент — ранний этап, а не неопытность</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Карточка с текстом</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>To pierwsze realizacje PAVLOV u klientów.
+Wchodzisz wtedy, kiedy stawka jeszcze nie urosła — a robota jest ta sama, którą widzisz na tym profilu.</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="63" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>STORIS</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Кружок OFERTA · 6</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Экономика в двух числах. Клиент считает выгоду сам</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Карточка с двумя цифрами, без графиков и без процентов</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Taki obiekt, składany przez kilka firm: 20–25 tysięcy.
+U mnie teraz: 13–18 tysięcy.
+Nie taniej za to samo. Taniej, bo między hurtownią a Twoją działką nikt nie dolicza swojego.</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>STORIS</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Кружок OFERTA · 7</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Дешёвый вход. Снять страх большой суммы</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Карточка + фото эскиза от руки</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Szkic koncepcyjny — 1000 zł.
+Rysunek, główne wymiary, orientacyjny koszt realizacji.
+Jeśli robimy dalej — kwota wchodzi w cenę.</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>STORIS</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Кружок OFERTA · 8</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Вход в разговор. Последняя карточка кружка</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Карточка с текстом на фоне вечернего кадра</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Masz pomysł? Napisz.
+Wystarczy jedno zdjęcie i kilka zdań o miejscu.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>STORIS</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
           <t>Кружок PROCES</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Снять страх неизвестности. Показать путь</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>4 карточки текстом, пока нет клиентов. После первого заказа переснять живьём</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>1) Piszesz i pokazujesz, co Ci się podoba
 2) Oglądam działkę, robię szkic
@@ -1307,134 +1599,135 @@
 4) Buduję i urządzam. Wchodzisz do gotowego</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="138.6" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>STORIS</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Кружок O MNIE</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Ядро позиционирования. Объяснить, почему один человек</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Происхождение бренда. Здесь НЕ продаём — на это есть OFERTA</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Фото себя за работой + карточки с текстом</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Zbudowałem to najpierw dla siebie — bo nie znalazłem takiego na rynku.
-Producenci żyją z powtarzalności. Studia sprzedają projekt i kończą. Stolarze żyją ze schodów.
-Dlatego prowadzę projekt sam: od pierwszego szkicu po ostatni detal.</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Jestem pierwszym klientem.
+Chciałem mieć u siebie miejsce, w którym wieczorem wystarczy usiąść i nigdzie nie jechać. Na rynku takiego nie było: albo konstrukcja do samodzielnego wykończenia, albo projekt bez wykonawcy.
+Więc zrobiłem sam — taras, domek dla córek, saunę. Uczyłem się na własnym podwórku, nie na cudzym.
+Zaczynam od siebie. Dosłownie.</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>STORIS</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Кружок ALTANY</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Накопительный. Собирается по ходу</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Лучшие кадры террасы из живых сторис — вечер, свет, использование</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Короткие подписи по ходу, без сценария</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>STORIS</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Кружок DOMKI</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Накопительный. Собирается по ходу</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Лучшие кадры домика — дети играют, вечерний свет, детали</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Короткие подписи по ходу, без сценария</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -1451,7 +1744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1490,7 +1783,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Сетка / лента / конкретный кружок</t>
+          <t>Сетка с номером позиции / лента / конкретный кружок</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1831,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Только для reels. Три типа: вопрос в комментарии · отсылка к профилю · призыв сохранить</t>
+          <t>Только для reels. Четыре типа: вопрос в комментарии · отсылка к профилю · призыв сохранить · → Oferta</t>
         </is>
       </c>
     </row>
@@ -1561,62 +1854,70 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>ПОРЯДОК ЗАПУСКА</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr"/>
+          <t>КОММЕРЧЕСКАЯ ОСЬ</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>День 1–3</t>
+          <t>Предложение</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Публиковать 2–3 в день с интервалом в несколько часов. Всё сразу — посты съедают охват друг друга</t>
+          <t>PAVLOV открывает 2–3 первых клиентских проекта на ближайшие полгода. Индивидуальный проект + полная реализация на стартовых условиях</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Хронология</t>
+          <t>Где оно живёт</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Переставить нельзя, новое встаёт слева вверху. Сильнейший кадр публиковать ПОСЛЕДНИМ</t>
+          <t>Явно — в посте №4 и в кружке OFERTA. Косвенно — в концовках reels, каждый раз другим углом. В сторис — напоминанием, сколько мест осталось</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Ритм сетки</t>
+          <t>Пропорция</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Общий план → деталь → люди → общий. Не два похожих подряд</t>
+          <t>70–80% доказательство: объекты, детали, решения, материалы. 20–30% предложение. Не подряд — предложение просто всегда доступно</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Дальше</t>
+          <t>Чего не делать</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>2 reels + 1 карусель в неделю. Сторис через день. Ключевое — отсутствие провалов, а не количество</t>
+          <t>Не называть проценты скидки. Не сравнивать с альтаной за 2 000 zł: это другой продукт. Сравнение — с ценой того же результата через цепочку</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr"/>
-      <c r="B15" s="9" t="inlineStr"/>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Не «я новичок»</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Аргумент цены не «дёшево, потому что без опыта», а «вход на раннем этапе, пока ставка не выросла»</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -1624,12 +1925,12 @@
           <t>ВАЖНО</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr"/>
+      <c r="B16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Reels остаётся навсегда</t>
+          <t>ПОРЯДОК ЗАПУСКА</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1641,24 +1942,120 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Обложка</t>
+          <t>Нумерация</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Для каждого reels выбрать обложку, иначе превью возьмётся из середины ролика и сломает сетку</t>
+          <t>№1–9 — позиции в сетке при чтении: слева сверху направо. Публиковать в ОБРАТНОМ порядке: №9 первым, №1 последним</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>Закрепить</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Позиции 1, 2 и 4: кто → что умеет → что предлагает</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>День 1–3</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Публиковать 2–3 в день с интервалом в несколько часов. Всё сразу — посты съедают охват друг друга</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Ритм сетки</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Общий план → деталь → люди → общий. Не два похожих подряд</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Дальше</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>2 reels + 1 карусель в неделю. Сторис через день. Ключевое — отсутствие провалов, а не количество</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Reels остаётся навсегда</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Любой reels попадает в сетку как обычный пост. Планка не ниже, чем для карусели</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Обложка</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Для каждого reels выбрать обложку, иначе превью возьмётся из середины ролика и сломает сетку</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Сохранения и переходы в директ. Не лайки и не подписчики</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Пока это правда</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Сторис «осталось 2 места» ставить, только пока мест действительно 2</t>
         </is>
       </c>
     </row>

--- a/Instagram/PAVLOV_content_plan.xlsx
+++ b/Instagram/PAVLOV_content_plan.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>«Zaczynam od siebie. Dosłownie.»</t>
+          <t>Последний кадр: «Zaczynam od siebie. Dosłownie.»</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>«Co byś tu dodał?»</t>
+          <t>Последний кадр: «Zostaje tylko usiąść.»</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>«Domek czy altana — co pierwsze?»</t>
+          <t>Последний кадр: «Domek można kupić. Własne miejsce — nie.»</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>«Masz pomysł? Napisz.»</t>
+          <t>Последний кадр: «Masz pomysł? Napisz — powiem, ile to kosztuje u Ciebie.»</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>«Zapisz, jeśli planujesz domek»</t>
+          <t>Последний кадр: «Tego nie widać. Widać za trzy lata.»</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>«Czego brakuje na Twoim tarasie?»</t>
+          <t>Последний кадр: «Nic do dokupienia. Nic do dokończenia.»</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>«Ile z tych sześciu masz już znalezionych?»</t>
+          <t>Последний кадр: «Ile z tych sześciu masz już znalezionych?» Отвечает в комментариях — отвечаю в личку. Единственный вопрос в сетке, и он здесь не для охвата</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>«Zapisz na wiosnę»</t>
+          <t>Последний кадр: «Tego nie widać. Ale bez tego korzenie marzną.»</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>«Wyślij swój obraz»</t>
+          <t>Последний кадр: «Wyślij swój obraz. Odpiszę, co da się z tego zrobić.»</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>«Co powinno być w saunie ogrodowej?»</t>
+          <t>Последний кадр: «Wnętrze pokażę, kiedy skończę.»</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>→ Oferta: «Masz pomysł? Zaprojektuję go pod Twoje miejsce i budżet.»</t>
+          <t>Финальный экран: «Wyślij swój obraz z Pinteresta. Odpiszę, jak to wygląda u Ciebie i za ile.»</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>→ Oferta: «Nie każdy wykonawca podejmie się takiego projektu.»</t>
+          <t>Финальный экран: «Chcesz taką ścianę u siebie? Napisz — powiem, gdzie to ma sens, a gdzie nie.»</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
+    <row r="14" ht="88.2" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>«Zapisz, zanim kupisz deski»</t>
+          <t>Финальный экран: «Zapisz, zanim kupisz deski.» / «A jak będziesz wybierać — napisz, dobiorę pod Twoje słońce.» Единственный ролик, где сохранение идёт раньше контакта</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>→ Oferta: «Pierwsze realizacje PAVLOV — zanim portfolio urośnie. Napisz.»</t>
+          <t>Финальный экран: «Wyślij zdjęcie swojej działki — policzę tak samo, na głos.»</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>→ Oferta: «Zaczynam od siebie. Teraz szukam kolejnych miejsc.»</t>
+          <t>Финальный экран: «Ile razy w roku wyjeżdżasz? Napisz — policzę, ile kosztuje nie jeździć.»</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>→ Oferta: «Jeden człowiek. Od pierwszego szkicu po montaż.»</t>
+          <t>Финальный экран: «Masz taras, który stoi pusty? Napisz — pokażę, co da się z nim zrobić.»</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Kto pierwszy napisze, ten wybiera termin.»</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Na którym z tych kroków zwykle się zatrzymujesz?»</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Reszta to mój problem, nie Twój.»</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Nietypowe nie znaczy droższe. Znaczy tyle, że mało kto to zrobi.»</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Za rok ta sama robota będzie kosztować inaczej.»</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Różnicę policz sam.»</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Najtańszy sposób, żeby zobaczyć to na papierze.»</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Napisz. Odpowiadam sam.» — единственная карточка кружка, которая просит</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Cztery kroki. Na każdym ta sama osoba.»</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Zaczynam od siebie. Teraz szukam kolejnych miejsc.»</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Wieczór, który nie wymaga przygotowań.»</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Drewno poczeka. Dzieciństwo nie.»</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Только для reels. Четыре типа: вопрос в комментарии · отсылка к профилю · призыв сохранить · → Oferta</t>
+          <t>Последний кадр карусели · финальный экран reels · последняя строка сторис. Делится не по формату, а по функции: доказательство закрывается утверждением и ничего не просит; предложение и reels просят написать и называют, что человек получит за сообщение; сторис дают повод подумать, просит только последняя карточка кружка</t>
         </is>
       </c>
     </row>
